--- a/KatalonData/Bootstrap/VSP-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VSP-Data-Prod.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\Bootstrap\"/>
     </mc:Choice>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="161">
   <si>
     <t>Notes</t>
   </si>
@@ -447,12 +447,76 @@
   </si>
   <si>
     <t>Tue Jul 07 16:34:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 09:50:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 10:12:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 10:35:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 10:57:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 11:20:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 07:53:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 08:15:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 08:38:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 09:00:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 09:23:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:05:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 03:35:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 03:50:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 04:07:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 04:25:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 04:31:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:51:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:53:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:55:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:56:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 06:58:36 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -785,47 +849,47 @@
   <dimension ref="A1:BA2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.3984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.73046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.73046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.1328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.73046875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.59765625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="3.9296875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="21" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="8.265625" bestFit="1" customWidth="1"/>
-    <col min="33" max="36" width="9" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.53125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7.9296875" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="7.73046875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="6.86328125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="8.3984375" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="21.9296875" bestFit="1" customWidth="1"/>
-    <col min="50" max="52" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="8.3984375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="24.33203125"/>
+    <col min="3" max="4" bestFit="true" customWidth="true" width="8.265625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="7.73046875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="8.73046875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="9.0"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="7.73046875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="8.9296875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="8.265625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="8.9296875"/>
+    <col min="12" max="13" bestFit="true" customWidth="true" width="8.265625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="4.33203125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="8.9296875"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="8.46484375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="8.796875"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="5.265625"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="7.33203125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="8.1328125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="7.1328125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="5.73046875"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="5.59765625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="3.9296875"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="21.0"/>
+    <col min="27" max="29" bestFit="true" customWidth="true" width="8.59765625"/>
+    <col min="30" max="32" bestFit="true" customWidth="true" width="8.265625"/>
+    <col min="33" max="36" bestFit="true" customWidth="true" width="9.0"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" width="9.53125"/>
+    <col min="38" max="38" bestFit="true" customWidth="true" width="8.46484375"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" width="7.9296875"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" width="8.9296875"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" width="8.796875"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" width="8.86328125"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" width="8.9296875"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" width="7.73046875"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" width="7.3984375"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" width="6.86328125"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" width="8.3984375"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" width="21.9296875"/>
+    <col min="50" max="52" bestFit="true" customWidth="true" width="8.59765625"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="9.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="28.5" x14ac:dyDescent="0.45">
@@ -990,13 +1054,13 @@
       </c>
     </row>
     <row r="2" spans="1:53" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="B2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>127</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -1056,7 +1120,7 @@
       </c>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
-      <c r="Z2" t="s">
+      <c r="Z2" t="s" s="0">
         <v>60</v>
       </c>
       <c r="AA2" s="1" t="s">
@@ -1125,7 +1189,7 @@
       <c r="AV2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AW2" t="s" s="0">
         <v>80</v>
       </c>
       <c r="AX2" s="1" t="s">
@@ -1286,13 +1350,13 @@
       </c>
     </row>
     <row r="2" spans="1:43" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="B2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>127</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -1352,7 +1416,7 @@
       </c>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
-      <c r="Z2" t="s">
+      <c r="Z2" t="s" s="0">
         <v>60</v>
       </c>
       <c r="AA2" s="1" t="s">
@@ -1546,13 +1610,13 @@
       </c>
     </row>
     <row r="2" spans="1:42" ht="57" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="B2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>127</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -1612,7 +1676,7 @@
       </c>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
-      <c r="Z2" t="s">
+      <c r="Z2" t="s" s="0">
         <v>60</v>
       </c>
       <c r="AA2" s="1" t="s">
@@ -1665,13 +1729,13 @@
       </c>
     </row>
     <row r="3" spans="1:42" ht="57" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>127</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -1731,7 +1795,7 @@
       </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
-      <c r="Z3" t="s">
+      <c r="Z3" t="s" s="0">
         <v>60</v>
       </c>
       <c r="AA3" s="1" t="s">
@@ -1784,13 +1848,13 @@
       </c>
     </row>
     <row r="4" spans="1:42" ht="57" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="B4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>127</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -1850,7 +1914,7 @@
       </c>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
-      <c r="Z4" t="s">
+      <c r="Z4" t="s" s="0">
         <v>60</v>
       </c>
       <c r="AA4" s="1" t="s">
